--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D67F21D7-B4B9-4672-9BBF-C91284209C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED89F48-0C4B-470B-A253-59492A061914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3465" yWindow="1260" windowWidth="19125" windowHeight="12315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quizzes" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="66">
   <si>
     <t>id</t>
   </si>
@@ -66,9 +66,6 @@
     <t>file</t>
   </si>
   <si>
-    <t>RH-GK1</t>
-  </si>
-  <si>
     <t>quizzes/Halloween_2026_Quiz.pdf</t>
   </si>
   <si>
@@ -99,12 +96,6 @@
     <t>Q0003</t>
   </si>
   <si>
-    <t>RH-GK2</t>
-  </si>
-  <si>
-    <t>RH-GK3</t>
-  </si>
-  <si>
     <t>25 Closing Lines from movies, but each letter in each word has been places in A-Z order.</t>
   </si>
   <si>
@@ -117,10 +108,145 @@
     <t>Q0004</t>
   </si>
   <si>
-    <t>RH-GK4</t>
-  </si>
-  <si>
     <t>Presidents of the USA</t>
+  </si>
+  <si>
+    <t>quizzes/Shakespeare_Sings_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Q0005</t>
+  </si>
+  <si>
+    <t>Shakespeare Sings</t>
+  </si>
+  <si>
+    <t>25 Song Lyrics but if Shakespeare had written them.</t>
+  </si>
+  <si>
+    <t>quizzes/OCD_Film_Quotes_01_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/OCD_Film_Quotes_02_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/OCD_Film_Quotes_03_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/OCD_Film_Quotes_04_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>OCD Film Quotes 01</t>
+  </si>
+  <si>
+    <t>OCD Film Quotes 02</t>
+  </si>
+  <si>
+    <t>OCD Film Quotes 03</t>
+  </si>
+  <si>
+    <t>OCD Film Quotes 04</t>
+  </si>
+  <si>
+    <t>Q0006</t>
+  </si>
+  <si>
+    <t>Q0007</t>
+  </si>
+  <si>
+    <t>Q0008</t>
+  </si>
+  <si>
+    <t>Q0009</t>
+  </si>
+  <si>
+    <t>25 Quotes from movies, but each letter in each word has been places in A-Z order.</t>
+  </si>
+  <si>
+    <t>quizzes/Poorly_Described_Films_01.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/Poorly_Described_Films_02.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/Poorly_Described_Films_03.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/Poorly_Described_Films_04.pdf</t>
+  </si>
+  <si>
+    <t>Poorly Described Films 01</t>
+  </si>
+  <si>
+    <t>Poorly Described Films 02</t>
+  </si>
+  <si>
+    <t>Poorly Described Films 03</t>
+  </si>
+  <si>
+    <t>Poorly Described Films 04</t>
+  </si>
+  <si>
+    <t>Q0010</t>
+  </si>
+  <si>
+    <t>Q0011</t>
+  </si>
+  <si>
+    <t>Q0012</t>
+  </si>
+  <si>
+    <t>Q0013</t>
+  </si>
+  <si>
+    <t>RH-GK001</t>
+  </si>
+  <si>
+    <t>RH-GK002</t>
+  </si>
+  <si>
+    <t>RH-GK003</t>
+  </si>
+  <si>
+    <t>RH-GK004</t>
+  </si>
+  <si>
+    <t>RH-GK005</t>
+  </si>
+  <si>
+    <t>RH-GK006</t>
+  </si>
+  <si>
+    <t>RH-GK007</t>
+  </si>
+  <si>
+    <t>RH-GK008</t>
+  </si>
+  <si>
+    <t>RH-GK009</t>
+  </si>
+  <si>
+    <t>RH-GK010</t>
+  </si>
+  <si>
+    <t>RH-GK011</t>
+  </si>
+  <si>
+    <t>RH-GK012</t>
+  </si>
+  <si>
+    <t>RH-GK013</t>
+  </si>
+  <si>
+    <t>25 Poorly Described Films</t>
+  </si>
+  <si>
+    <t>26 Poorly Described Films</t>
+  </si>
+  <si>
+    <t>27 Poorly Described Films</t>
+  </si>
+  <si>
+    <t>28 Poorly Described Films</t>
   </si>
 </sst>
 </file>
@@ -501,12 +627,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="61" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="32" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9.140625" style="2"/>
@@ -531,70 +657,223 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="E4" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>19</v>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED89F48-0C4B-470B-A253-59492A061914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD81345-832A-4398-8149-2F82B4A55EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3465" yWindow="1260" windowWidth="19125" windowHeight="12315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quizzes" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="96">
   <si>
     <t>id</t>
   </si>
@@ -162,18 +163,6 @@
     <t>25 Quotes from movies, but each letter in each word has been places in A-Z order.</t>
   </si>
   <si>
-    <t>quizzes/Poorly_Described_Films_01.pdf</t>
-  </si>
-  <si>
-    <t>quizzes/Poorly_Described_Films_02.pdf</t>
-  </si>
-  <si>
-    <t>quizzes/Poorly_Described_Films_03.pdf</t>
-  </si>
-  <si>
-    <t>quizzes/Poorly_Described_Films_04.pdf</t>
-  </si>
-  <si>
     <t>Poorly Described Films 01</t>
   </si>
   <si>
@@ -247,6 +236,108 @@
   </si>
   <si>
     <t>28 Poorly Described Films</t>
+  </si>
+  <si>
+    <t>quizzes/Poorly_Described_Films_04_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/Poorly_Described_Films_03_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/Poorly_Described_Films_02_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/Poorly_Described_Films_01_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>American actor known for laid-back comedic roles in films such as Wedding Crashers.</t>
+  </si>
+  <si>
+    <t>British actress celebrated for roles in Downton Abbey and the Harry Potter films.</t>
+  </si>
+  <si>
+    <t>American actor known for starring in films like Fight Club, Se7en, and Ocean’s Eleven.</t>
+  </si>
+  <si>
+    <t>English actor best known for portraying a modern, gritty version of James Bond.</t>
+  </si>
+  <si>
+    <t>American actress globally recognised for her role in the sitcom Friends.</t>
+  </si>
+  <si>
+    <t>French actor known for intense performances in films like Léon: The Professional.</t>
+  </si>
+  <si>
+    <t>American actress famous for her work in horror classics and recent award-winning films.</t>
+  </si>
+  <si>
+    <t>American actor and director known for westerns, action films, and acclaimed dramas.</t>
+  </si>
+  <si>
+    <t>British actor with a decades-long career, appearing in classics like The Italian Job.</t>
+  </si>
+  <si>
+    <t>British actress known for acclaimed performances in The Queen and Prime Suspect.</t>
+  </si>
+  <si>
+    <t>American actress famous for major roles in The Devil Wears Prada and Les Misérables.</t>
+  </si>
+  <si>
+    <t>American actor who won an Academy Award for a powerful performance in The Pianist.</t>
+  </si>
+  <si>
+    <t>Canadian singer celebrated worldwide for her powerhouse vocals and iconic ballads.</t>
+  </si>
+  <si>
+    <t>Canadian-American actor best known for deadpan comedy in Airplane! and The Naked Gun.</t>
+  </si>
+  <si>
+    <t>American actress recognised for starring in As Good as It Gets and Mad About You.</t>
+  </si>
+  <si>
+    <t>Ukrainian president who previously worked as a comedian and television actor.</t>
+  </si>
+  <si>
+    <t>British author who created the globally successful Harry Potter book series.</t>
+  </si>
+  <si>
+    <t>Italian tenor renowned for his classical and crossover performances.</t>
+  </si>
+  <si>
+    <t>American actress best known for leading the hit series Sex and the City.</t>
+  </si>
+  <si>
+    <t>American rock musician nicknamed “The Boss,” famous for anthems like Born to Run.</t>
+  </si>
+  <si>
+    <t>American actor with a legendary voice, famously portraying Darth Vader in Star Wars.</t>
+  </si>
+  <si>
+    <t>British actress known for transformative, unconventional roles in films like Michael Clayton.</t>
+  </si>
+  <si>
+    <t>American actress known for standout roles in Scarface, Batman Returns, and The Fabulous Baker Boys.</t>
+  </si>
+  <si>
+    <t>American actor known for quirky roles in films like Fargo and the series Boardwalk Empire.</t>
+  </si>
+  <si>
+    <t>British-American actress celebrated for her long career in television, film, and theatre.</t>
+  </si>
+  <si>
+    <t>Caricature</t>
+  </si>
+  <si>
+    <t>Q0014</t>
+  </si>
+  <si>
+    <t>RH-GK014</t>
+  </si>
+  <si>
+    <t>25 Caricature of Celebrities</t>
+  </si>
+  <si>
+    <t>quizzes/Caricature_Quiz.pdf</t>
   </si>
 </sst>
 </file>
@@ -627,7 +718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
@@ -663,7 +754,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>8</v>
@@ -680,7 +771,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>15</v>
@@ -697,7 +788,7 @@
         <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
@@ -714,7 +805,7 @@
         <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>17</v>
@@ -731,7 +822,7 @@
         <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>23</v>
@@ -748,7 +839,7 @@
         <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>36</v>
@@ -765,7 +856,7 @@
         <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>36</v>
@@ -782,7 +873,7 @@
         <v>30</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>36</v>
@@ -799,7 +890,7 @@
         <v>31</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>36</v>
@@ -810,70 +901,87 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="E11" s="2" t="s">
-        <v>37</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="E12" s="2" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="E13" s="2" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="E14" s="2" t="s">
-        <v>40</v>
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -882,4 +990,221 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82C210C4-D93A-4FC9-80AF-597D4141A3D6}">
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="93.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>9</v>
+      </c>
+      <c r="B9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>13</v>
+      </c>
+      <c r="B13" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>24</v>
+      </c>
+      <c r="B24" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:A25">
+    <sortCondition ref="A1:A25"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
 </file>
--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD81345-832A-4398-8149-2F82B4A55EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{398054FA-3A5A-4729-9813-351D88C6E85D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3465" yWindow="1260" windowWidth="19125" windowHeight="12315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quizzes" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -73,9 +72,6 @@
     <t>Q0001</t>
   </si>
   <si>
-    <t>Halowween 2026</t>
-  </si>
-  <si>
     <t>28 Images of Famous Personalities with a Haloween theme.</t>
   </si>
   <si>
@@ -250,81 +246,6 @@
     <t>quizzes/Poorly_Described_Films_01_Quiz.pdf</t>
   </si>
   <si>
-    <t>American actor known for laid-back comedic roles in films such as Wedding Crashers.</t>
-  </si>
-  <si>
-    <t>British actress celebrated for roles in Downton Abbey and the Harry Potter films.</t>
-  </si>
-  <si>
-    <t>American actor known for starring in films like Fight Club, Se7en, and Ocean’s Eleven.</t>
-  </si>
-  <si>
-    <t>English actor best known for portraying a modern, gritty version of James Bond.</t>
-  </si>
-  <si>
-    <t>American actress globally recognised for her role in the sitcom Friends.</t>
-  </si>
-  <si>
-    <t>French actor known for intense performances in films like Léon: The Professional.</t>
-  </si>
-  <si>
-    <t>American actress famous for her work in horror classics and recent award-winning films.</t>
-  </si>
-  <si>
-    <t>American actor and director known for westerns, action films, and acclaimed dramas.</t>
-  </si>
-  <si>
-    <t>British actor with a decades-long career, appearing in classics like The Italian Job.</t>
-  </si>
-  <si>
-    <t>British actress known for acclaimed performances in The Queen and Prime Suspect.</t>
-  </si>
-  <si>
-    <t>American actress famous for major roles in The Devil Wears Prada and Les Misérables.</t>
-  </si>
-  <si>
-    <t>American actor who won an Academy Award for a powerful performance in The Pianist.</t>
-  </si>
-  <si>
-    <t>Canadian singer celebrated worldwide for her powerhouse vocals and iconic ballads.</t>
-  </si>
-  <si>
-    <t>Canadian-American actor best known for deadpan comedy in Airplane! and The Naked Gun.</t>
-  </si>
-  <si>
-    <t>American actress recognised for starring in As Good as It Gets and Mad About You.</t>
-  </si>
-  <si>
-    <t>Ukrainian president who previously worked as a comedian and television actor.</t>
-  </si>
-  <si>
-    <t>British author who created the globally successful Harry Potter book series.</t>
-  </si>
-  <si>
-    <t>Italian tenor renowned for his classical and crossover performances.</t>
-  </si>
-  <si>
-    <t>American actress best known for leading the hit series Sex and the City.</t>
-  </si>
-  <si>
-    <t>American rock musician nicknamed “The Boss,” famous for anthems like Born to Run.</t>
-  </si>
-  <si>
-    <t>American actor with a legendary voice, famously portraying Darth Vader in Star Wars.</t>
-  </si>
-  <si>
-    <t>British actress known for transformative, unconventional roles in films like Michael Clayton.</t>
-  </si>
-  <si>
-    <t>American actress known for standout roles in Scarface, Batman Returns, and The Fabulous Baker Boys.</t>
-  </si>
-  <si>
-    <t>American actor known for quirky roles in films like Fargo and the series Boardwalk Empire.</t>
-  </si>
-  <si>
-    <t>British-American actress celebrated for her long career in television, film, and theatre.</t>
-  </si>
-  <si>
     <t>Caricature</t>
   </si>
   <si>
@@ -338,6 +259,84 @@
   </si>
   <si>
     <t>quizzes/Caricature_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/Halloween_(Jacks)_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Q0015</t>
+  </si>
+  <si>
+    <t>RH-GK015</t>
+  </si>
+  <si>
+    <t>Halloween (Jacks)</t>
+  </si>
+  <si>
+    <t>25 Images of People who's names contain 'Jack' - Hidden behind a Jack-O-Lantern</t>
+  </si>
+  <si>
+    <t>Q0016</t>
+  </si>
+  <si>
+    <t>RH-GK016</t>
+  </si>
+  <si>
+    <t>Halloween (Vamp Theme)</t>
+  </si>
+  <si>
+    <t>25 Haloween / Vamp themed images.</t>
+  </si>
+  <si>
+    <t>RH-GK017</t>
+  </si>
+  <si>
+    <t>RH-GK018</t>
+  </si>
+  <si>
+    <t>Q0017</t>
+  </si>
+  <si>
+    <t>Q0018</t>
+  </si>
+  <si>
+    <t>Marvel Villians</t>
+  </si>
+  <si>
+    <t>Marvel Villians (Tiled)</t>
+  </si>
+  <si>
+    <t>25 Images of Actors who have played a Marvel Villian</t>
+  </si>
+  <si>
+    <t>25 Images of Actors who have played a Marvel Villian (Images Spliced and Tiled)</t>
+  </si>
+  <si>
+    <t>Halloween 2026</t>
+  </si>
+  <si>
+    <t>Halloween (Witches)</t>
+  </si>
+  <si>
+    <t>RH-GK019</t>
+  </si>
+  <si>
+    <t>Q0019</t>
+  </si>
+  <si>
+    <t>28 Images of Witches</t>
+  </si>
+  <si>
+    <t>quizzes/Halloween_(Vamp_Theme)_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/Halloween_(Witches)_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/Marvel_Villains_(Tiled)_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/Marvel_Villains_Quiz.pdf</t>
   </si>
 </sst>
 </file>
@@ -718,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
@@ -750,31 +749,31 @@
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>7</v>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>9</v>
@@ -782,67 +781,67 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>24</v>
@@ -850,16 +849,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>25</v>
@@ -867,16 +866,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>26</v>
@@ -884,103 +883,188 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>58</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>39</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>60</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B15" s="2" t="s">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="E18" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D15" s="2" t="s">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E15" s="2" t="s">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>95</v>
       </c>
     </row>
@@ -990,221 +1074,4 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82C210C4-D93A-4FC9-80AF-597D4141A3D6}">
-  <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="93.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>10</v>
-      </c>
-      <c r="B10" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>11</v>
-      </c>
-      <c r="B11" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>12</v>
-      </c>
-      <c r="B12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>13</v>
-      </c>
-      <c r="B13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>16</v>
-      </c>
-      <c r="B16" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>17</v>
-      </c>
-      <c r="B17" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>18</v>
-      </c>
-      <c r="B18" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>19</v>
-      </c>
-      <c r="B19" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>20</v>
-      </c>
-      <c r="B20" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>21</v>
-      </c>
-      <c r="B21" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>22</v>
-      </c>
-      <c r="B22" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>23</v>
-      </c>
-      <c r="B23" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>24</v>
-      </c>
-      <c r="B24" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>25</v>
-      </c>
-      <c r="B25" t="s">
-        <v>86</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:A25">
-    <sortCondition ref="A1:A25"/>
-  </sortState>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-</worksheet>
 </file>
--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{398054FA-3A5A-4729-9813-351D88C6E85D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E41D4F9-36C3-42D8-9D03-63942A0D5001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6690" yWindow="3165" windowWidth="19125" windowHeight="12315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quizzes" sheetId="1" r:id="rId1"/>
@@ -1048,7 +1048,7 @@
         <v>85</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -1065,7 +1065,7 @@
         <v>86</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E41D4F9-36C3-42D8-9D03-63942A0D5001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD6250E-4065-4574-816A-D4762E3F26BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6690" yWindow="3165" windowWidth="19125" windowHeight="12315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quizzes" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="101">
   <si>
     <t>id</t>
   </si>
@@ -337,6 +337,21 @@
   </si>
   <si>
     <t>quizzes/Marvel_Villains_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/Nazis_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Q0020</t>
+  </si>
+  <si>
+    <t>RH-GK020</t>
+  </si>
+  <si>
+    <t>Nazis</t>
+  </si>
+  <si>
+    <t>25 Images of Celebrities dressed as Nazis</t>
   </si>
 </sst>
 </file>
@@ -717,7 +732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
@@ -1068,6 +1083,23 @@
         <v>94</v>
       </c>
     </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD6250E-4065-4574-816A-D4762E3F26BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A9BBDF-3B7B-4855-A00C-C4D46B9BAC7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="106">
   <si>
     <t>id</t>
   </si>
@@ -352,6 +352,21 @@
   </si>
   <si>
     <t>25 Images of Celebrities dressed as Nazis</t>
+  </si>
+  <si>
+    <t>Acting is a Drag</t>
+  </si>
+  <si>
+    <t>25 Images of Celebrities dressed as the opposite sex.</t>
+  </si>
+  <si>
+    <t>Q0021</t>
+  </si>
+  <si>
+    <t>RH-GK021</t>
+  </si>
+  <si>
+    <t>quizzes/Acting_is_a_Drag_Quiz.pdf</t>
   </si>
 </sst>
 </file>
@@ -732,7 +747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
@@ -1097,6 +1112,23 @@
         <v>100</v>
       </c>
       <c r="E21" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>96</v>
       </c>
     </row>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A9BBDF-3B7B-4855-A00C-C4D46B9BAC7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C34742A-75D6-4086-999E-D35432FFD424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="111">
   <si>
     <t>id</t>
   </si>
@@ -367,6 +367,21 @@
   </si>
   <si>
     <t>quizzes/Acting_is_a_Drag_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/Classic_Adverts_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Q0022</t>
+  </si>
+  <si>
+    <t>RH-GK022</t>
+  </si>
+  <si>
+    <t>Classic Adverts</t>
+  </si>
+  <si>
+    <t>25 Images of Classic Adverts - Name the Product / Company.</t>
   </si>
 </sst>
 </file>
@@ -747,7 +762,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
@@ -1129,6 +1144,23 @@
         <v>102</v>
       </c>
       <c r="E22" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>96</v>
       </c>
     </row>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C34742A-75D6-4086-999E-D35432FFD424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29F7420C-3764-4247-80AB-87EAFB0C488A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quizzes" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="151">
   <si>
     <t>id</t>
   </si>
@@ -382,6 +383,126 @@
   </si>
   <si>
     <t>25 Images of Classic Adverts - Name the Product / Company.</t>
+  </si>
+  <si>
+    <t>quizzes/Clergy_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>25 Images of Celebrities dressed as Clergy.</t>
+  </si>
+  <si>
+    <t>Clergy</t>
+  </si>
+  <si>
+    <t>Q0023</t>
+  </si>
+  <si>
+    <t>RH-GK023</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\05 - Damian Lewis.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\06 - Barbara Knox.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\07 - Rupert Grint.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\08 - Stacey Dooley.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\09 - Winston Churchill.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\10 - Julianne Moore.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\11 - Ron Howard.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\12 - Lindsay Lohan.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\13 - Michael Fassbender.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\14 - Molly Ringwald..png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\15 - Ben Stokes.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\16 - Rose Leslie.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\17 - Mick Hucknall.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\18 - Nicole Kidman.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\19 - James Hewitt.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\20 - Charlie Dimmock.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\21 - Greg Rutherford.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\22 - Isla Fisher.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\23 - Morgan Sam Lee Burtwistle.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\24 - Jessica Chastain.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\25 - Domhnall Gleeson.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\01 - Brendan Gleeson.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\02 - Karen Gillan.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\03 - Conan O'Brien.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\04 - Christina Hendricks.png</t>
+  </si>
+  <si>
+    <t>Q0024</t>
+  </si>
+  <si>
+    <t>RH-GK024</t>
+  </si>
+  <si>
+    <t>Redheads</t>
+  </si>
+  <si>
+    <t>quizzes/Readheads_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>25 Images of Celebrities Redheads.</t>
+  </si>
+  <si>
+    <t>quizzes/Chorus_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Chorus</t>
+  </si>
+  <si>
+    <t>Q0025</t>
+  </si>
+  <si>
+    <t>RH-GK025</t>
+  </si>
+  <si>
+    <t>Name the artist from the song chorus, words that appear in the title have been replaced with a 'Note' and vowels replaced by a 'Dash'.</t>
   </si>
 </sst>
 </file>
@@ -436,7 +557,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -444,20 +565,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -762,31 +899,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="61" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="93.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -794,16 +931,16 @@
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -811,16 +948,16 @@
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -828,16 +965,16 @@
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="4" t="s">
         <v>15</v>
       </c>
     </row>
@@ -845,16 +982,16 @@
       <c r="A5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="4" t="s">
         <v>19</v>
       </c>
     </row>
@@ -862,16 +999,16 @@
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="4" t="s">
         <v>23</v>
       </c>
     </row>
@@ -879,16 +1016,16 @@
       <c r="A7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="4" t="s">
         <v>24</v>
       </c>
     </row>
@@ -896,16 +1033,16 @@
       <c r="A8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="4" t="s">
         <v>29</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="4" t="s">
         <v>25</v>
       </c>
     </row>
@@ -913,16 +1050,16 @@
       <c r="A9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="4" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="4" t="s">
         <v>26</v>
       </c>
     </row>
@@ -930,16 +1067,16 @@
       <c r="A10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="4" t="s">
         <v>64</v>
       </c>
     </row>
@@ -947,16 +1084,16 @@
       <c r="A11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="4" t="s">
         <v>63</v>
       </c>
     </row>
@@ -964,16 +1101,16 @@
       <c r="A12" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="4" t="s">
         <v>38</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="4" t="s">
         <v>62</v>
       </c>
     </row>
@@ -981,16 +1118,16 @@
       <c r="A13" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="4" t="s">
         <v>61</v>
       </c>
     </row>
@@ -998,16 +1135,16 @@
       <c r="A14" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="4" t="s">
         <v>65</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="4" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1021,7 +1158,7 @@
       <c r="C15" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E15" s="3" t="s">
@@ -1032,16 +1169,16 @@
       <c r="A16" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="4" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1049,16 +1186,16 @@
       <c r="A17" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="4" t="s">
         <v>77</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="4" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1066,16 +1203,16 @@
       <c r="A18" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="4" t="s">
         <v>88</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="4" t="s">
         <v>93</v>
       </c>
     </row>
@@ -1083,16 +1220,16 @@
       <c r="A19" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="4" t="s">
         <v>83</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="4" t="s">
         <v>95</v>
       </c>
     </row>
@@ -1100,16 +1237,16 @@
       <c r="A20" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="4" t="s">
         <v>84</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="4" t="s">
         <v>94</v>
       </c>
     </row>
@@ -1117,33 +1254,33 @@
       <c r="A21" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="4" t="s">
         <v>99</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>105</v>
+      <c r="E21" s="4" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="4" t="s">
         <v>101</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="4" t="s">
         <v>106</v>
       </c>
     </row>
@@ -1151,17 +1288,68 @@
       <c r="A23" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="4" t="s">
         <v>109</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>96</v>
+      <c r="E23" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -1170,4 +1358,142 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D09740C-5E91-4C19-80AE-8B0F80234D77}">
+  <dimension ref="A1:A25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>136</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:A25">
+    <sortCondition ref="A1:A25"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,15 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29F7420C-3764-4247-80AB-87EAFB0C488A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB55802D-A7B4-4151-9D1E-EC49FB0B87F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quizzes" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -50,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="131">
   <si>
     <t>id</t>
   </si>
@@ -400,81 +399,6 @@
     <t>RH-GK023</t>
   </si>
   <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\05 - Damian Lewis.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\06 - Barbara Knox.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\07 - Rupert Grint.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\08 - Stacey Dooley.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\09 - Winston Churchill.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\10 - Julianne Moore.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\11 - Ron Howard.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\12 - Lindsay Lohan.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\13 - Michael Fassbender.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\14 - Molly Ringwald..png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\15 - Ben Stokes.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\16 - Rose Leslie.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\17 - Mick Hucknall.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\18 - Nicole Kidman.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\19 - James Hewitt.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\20 - Charlie Dimmock.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\21 - Greg Rutherford.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\22 - Isla Fisher.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\23 - Morgan Sam Lee Burtwistle.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\24 - Jessica Chastain.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\25 - Domhnall Gleeson.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\01 - Brendan Gleeson.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\02 - Karen Gillan.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\03 - Conan O'Brien.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\Cleaned\xx - Red Heads\Pictures\04 - Christina Hendricks.png</t>
-  </si>
-  <si>
     <t>Q0024</t>
   </si>
   <si>
@@ -503,6 +427,21 @@
   </si>
   <si>
     <t>Name the artist from the song chorus, words that appear in the title have been replaced with a 'Note' and vowels replaced by a 'Dash'.</t>
+  </si>
+  <si>
+    <t>Q0026</t>
+  </si>
+  <si>
+    <t>RH-GK026</t>
+  </si>
+  <si>
+    <t>quizzes/Name_That_Tune_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>That That Tune</t>
+  </si>
+  <si>
+    <t>25 Cryptic Songs and Artists</t>
   </si>
 </sst>
 </file>
@@ -899,7 +838,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -1320,36 +1259,53 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>146</v>
+        <v>121</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -1358,142 +1314,4 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D09740C-5E91-4C19-80AE-8B0F80234D77}">
-  <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>136</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:A25">
-    <sortCondition ref="A1:A25"/>
-  </sortState>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB55802D-A7B4-4151-9D1E-EC49FB0B87F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5EB3FAE-86B2-45BE-84E4-97AF844A9A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1220,7 +1220,7 @@
         <v>102</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
@@ -1237,7 +1237,7 @@
         <v>110</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5EB3FAE-86B2-45BE-84E4-97AF844A9A87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1896C1C-BD3E-4787-8D9A-C7F85E9CBA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="136">
   <si>
     <t>id</t>
   </si>
@@ -442,6 +442,21 @@
   </si>
   <si>
     <t>25 Cryptic Songs and Artists</t>
+  </si>
+  <si>
+    <t>Q0027</t>
+  </si>
+  <si>
+    <t>RH-GK027</t>
+  </si>
+  <si>
+    <t>quizzes/Film_Dingbats_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Film Dingbats</t>
+  </si>
+  <si>
+    <t>25 Cryptic Images of Popular Films</t>
   </si>
 </sst>
 </file>
@@ -838,7 +853,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -1308,6 +1323,23 @@
         <v>128</v>
       </c>
     </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1896C1C-BD3E-4787-8D9A-C7F85E9CBA7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50634042-7D5D-4889-9D7A-E222BC68FEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="159">
   <si>
     <t>id</t>
   </si>
@@ -457,6 +457,75 @@
   </si>
   <si>
     <t>25 Cryptic Images of Popular Films</t>
+  </si>
+  <si>
+    <t>Q0028</t>
+  </si>
+  <si>
+    <t>RH-GK028</t>
+  </si>
+  <si>
+    <t>Kens Quiz</t>
+  </si>
+  <si>
+    <t>25 Name The Celebrity Images. All either contain the name "Ken" or are known for playing a character with "Ken" in the name.</t>
+  </si>
+  <si>
+    <t>quizzes/Kens_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Q0029</t>
+  </si>
+  <si>
+    <t>RH-GK029</t>
+  </si>
+  <si>
+    <t>Q0030</t>
+  </si>
+  <si>
+    <t>RH-GK030</t>
+  </si>
+  <si>
+    <t>quizzes/Michaels_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/Michaels_(Tiled)_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>25 Name The Celebrity Images.</t>
+  </si>
+  <si>
+    <t>25 Name The Celebrity Images (Images Spliced and Tiled)</t>
+  </si>
+  <si>
+    <t>Michaels</t>
+  </si>
+  <si>
+    <t>Michaels (Tiled)</t>
+  </si>
+  <si>
+    <t>Q0031</t>
+  </si>
+  <si>
+    <t>RH-GK031</t>
+  </si>
+  <si>
+    <t>quizzes/Robs_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Q0032</t>
+  </si>
+  <si>
+    <t>RH-GK032</t>
+  </si>
+  <si>
+    <t>Who's Behind The Mask</t>
+  </si>
+  <si>
+    <t>25 Images of Actors wearing face coverings in roles. Just name the Actor.</t>
+  </si>
+  <si>
+    <t>quizzes/Who's_Behind_The_Mask_Quiz.pdf</t>
   </si>
 </sst>
 </file>
@@ -853,11 +922,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="93.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="32" style="1" bestFit="1" customWidth="1"/>
@@ -1340,6 +1409,91 @@
         <v>133</v>
       </c>
     </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50634042-7D5D-4889-9D7A-E222BC68FEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BA9934-4923-4337-AFAE-9F45A59AEA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1515" yWindow="1515" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quizzes" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="160">
   <si>
     <t>id</t>
   </si>
@@ -526,6 +526,9 @@
   </si>
   <si>
     <t>quizzes/Who's_Behind_The_Mask_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Robs</t>
   </si>
 </sst>
 </file>
@@ -1465,7 +1468,7 @@
         <v>151</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>152</v>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23BA9934-4923-4337-AFAE-9F45A59AEA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BE03D5-104E-4F76-BB92-C58B4BE61AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1515" yWindow="1515" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="165">
   <si>
     <t>id</t>
   </si>
@@ -529,6 +529,21 @@
   </si>
   <si>
     <t>Robs</t>
+  </si>
+  <si>
+    <t>quizzes/Film_Objects_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Q0033</t>
+  </si>
+  <si>
+    <t>RH-GK033</t>
+  </si>
+  <si>
+    <t>Film Objects</t>
+  </si>
+  <si>
+    <t>25 Images of Objects in Film. Just name the Film.</t>
   </si>
 </sst>
 </file>
@@ -925,7 +940,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -1497,6 +1512,23 @@
         <v>158</v>
       </c>
     </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BE03D5-104E-4F76-BB92-C58B4BE61AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90CA9F07-A22C-4587-A06F-809E4435DEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="1515" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quizzes" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="185">
   <si>
     <t>id</t>
   </si>
@@ -544,6 +544,66 @@
   </si>
   <si>
     <t>25 Images of Objects in Film. Just name the Film.</t>
+  </si>
+  <si>
+    <t>quizzes/Rebus_The_Bands_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Q0034</t>
+  </si>
+  <si>
+    <t>RH-GK034</t>
+  </si>
+  <si>
+    <t>Rebus "The" Bands</t>
+  </si>
+  <si>
+    <t>quizzes/Rebus_Sidekicks_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Q0035</t>
+  </si>
+  <si>
+    <t>RH-GK035</t>
+  </si>
+  <si>
+    <t>Rebus Sidekicks</t>
+  </si>
+  <si>
+    <t>25 Rebus Images of just the Sidekick - Name the Sidekick and their Main Character/Partner</t>
+  </si>
+  <si>
+    <t>25 Rebus Images of "The" Bands. Each image is a visual pun or clue that represents a band name.</t>
+  </si>
+  <si>
+    <t>Q0036</t>
+  </si>
+  <si>
+    <t>RH-GK036</t>
+  </si>
+  <si>
+    <t>quizzes/Soap_Characters_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Soap Characters</t>
+  </si>
+  <si>
+    <t>25 Images. Combine the left image’s first name with the right image’s last name to make a soap character.</t>
+  </si>
+  <si>
+    <t>Q0037</t>
+  </si>
+  <si>
+    <t>RH-GK037</t>
+  </si>
+  <si>
+    <t>quizzes/1%_Club.pdf</t>
+  </si>
+  <si>
+    <t>1% Club</t>
+  </si>
+  <si>
+    <t>25 Images of 1% Club Puzzles.</t>
   </si>
 </sst>
 </file>
@@ -940,7 +1000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -1529,6 +1589,74 @@
         <v>160</v>
       </c>
     </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90CA9F07-A22C-4587-A06F-809E4435DEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FBB9587-F5BE-4EB6-98CB-BF5F32887C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -597,13 +597,13 @@
     <t>RH-GK037</t>
   </si>
   <si>
-    <t>quizzes/1%_Club.pdf</t>
-  </si>
-  <si>
     <t>1% Club</t>
   </si>
   <si>
     <t>25 Images of 1% Club Puzzles.</t>
+  </si>
+  <si>
+    <t>quizzes/1_Percent_Club.pdf</t>
   </si>
 </sst>
 </file>
@@ -1645,16 +1645,16 @@
         <v>180</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>181</v>
       </c>
       <c r="D38" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E38" s="4" t="s">
         <v>184</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FBB9587-F5BE-4EB6-98CB-BF5F32887C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D4A941-9B0F-4026-ABDD-AB8EE2A7598E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="200">
   <si>
     <t>id</t>
   </si>
@@ -306,12 +306,6 @@
     <t>Marvel Villians (Tiled)</t>
   </si>
   <si>
-    <t>25 Images of Actors who have played a Marvel Villian</t>
-  </si>
-  <si>
-    <t>25 Images of Actors who have played a Marvel Villian (Images Spliced and Tiled)</t>
-  </si>
-  <si>
     <t>Halloween 2026</t>
   </si>
   <si>
@@ -324,9 +318,6 @@
     <t>Q0019</t>
   </si>
   <si>
-    <t>28 Images of Witches</t>
-  </si>
-  <si>
     <t>quizzes/Halloween_(Vamp_Theme)_Quiz.pdf</t>
   </si>
   <si>
@@ -351,9 +342,6 @@
     <t>Nazis</t>
   </si>
   <si>
-    <t>25 Images of Celebrities dressed as Nazis</t>
-  </si>
-  <si>
     <t>Acting is a Drag</t>
   </si>
   <si>
@@ -441,9 +429,6 @@
     <t>That That Tune</t>
   </si>
   <si>
-    <t>25 Cryptic Songs and Artists</t>
-  </si>
-  <si>
     <t>Q0027</t>
   </si>
   <si>
@@ -456,9 +441,6 @@
     <t>Film Dingbats</t>
   </si>
   <si>
-    <t>25 Cryptic Images of Popular Films</t>
-  </si>
-  <si>
     <t>Q0028</t>
   </si>
   <si>
@@ -495,9 +477,6 @@
     <t>25 Name The Celebrity Images.</t>
   </si>
   <si>
-    <t>25 Name The Celebrity Images (Images Spliced and Tiled)</t>
-  </si>
-  <si>
     <t>Michaels</t>
   </si>
   <si>
@@ -570,9 +549,6 @@
     <t>Rebus Sidekicks</t>
   </si>
   <si>
-    <t>25 Rebus Images of just the Sidekick - Name the Sidekick and their Main Character/Partner</t>
-  </si>
-  <si>
     <t>25 Rebus Images of "The" Bands. Each image is a visual pun or clue that represents a band name.</t>
   </si>
   <si>
@@ -604,6 +580,75 @@
   </si>
   <si>
     <t>quizzes/1_Percent_Club.pdf</t>
+  </si>
+  <si>
+    <t>Q0038</t>
+  </si>
+  <si>
+    <t>RH-GK038</t>
+  </si>
+  <si>
+    <t>Q0039</t>
+  </si>
+  <si>
+    <t>RH-GK039</t>
+  </si>
+  <si>
+    <t>Rear of the Year</t>
+  </si>
+  <si>
+    <t>Rear of the Year (Tiled)</t>
+  </si>
+  <si>
+    <t>quizzes/Rear_of_the_Year_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/Rear_of_the_Year_(Tiled)_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>25 Images of Celebrities who have won Rear of the Year.</t>
+  </si>
+  <si>
+    <t>25 Images of Celebrities who have won Rear of the Year  (Images Spliced and Tiled).</t>
+  </si>
+  <si>
+    <t>25 Rebus Images of just the Sidekick - Name the Sidekick and their Main Character/Partner.</t>
+  </si>
+  <si>
+    <t>25 Name The Celebrity Images (Images Spliced and Tiled).</t>
+  </si>
+  <si>
+    <t>25 Cryptic Images of Popular Films.</t>
+  </si>
+  <si>
+    <t>25 Cryptic Songs and Artists.</t>
+  </si>
+  <si>
+    <t>25 Images of Celebrities dressed as Nazis.</t>
+  </si>
+  <si>
+    <t>25 Images of Actors who have played a Marvel Villian (Images Spliced and Tiled).</t>
+  </si>
+  <si>
+    <t>25 Images of Actors who have played a Marvel Villian.</t>
+  </si>
+  <si>
+    <t>28 Images of Witches.</t>
+  </si>
+  <si>
+    <t>quizzes/High_Brow_Low_Brow_(Cartoons_and_Art)_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Q0040</t>
+  </si>
+  <si>
+    <t>RH-GK040</t>
+  </si>
+  <si>
+    <t>High Brow Low Brow (Cartoons and Art)</t>
+  </si>
+  <si>
+    <t>25 Images. Name the Cartoon from the Silhouette, also the Famous Artwork, and the Artwork's Artist.</t>
   </si>
 </sst>
 </file>
@@ -1000,14 +1045,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="93.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -1254,7 +1299,7 @@
         <v>66</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>67</v>
@@ -1297,7 +1342,7 @@
         <v>78</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -1305,16 +1350,16 @@
         <v>81</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>79</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>91</v>
+        <v>194</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -1328,333 +1373,384 @@
         <v>80</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>85</v>
+        <v>193</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>84</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>86</v>
+        <v>192</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>100</v>
+        <v>191</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>120</v>
-      </c>
       <c r="E25" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>135</v>
+        <v>189</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>147</v>
-      </c>
       <c r="E30" s="4" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>150</v>
-      </c>
       <c r="C31" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>148</v>
+        <v>188</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>174</v>
-      </c>
       <c r="E35" s="4" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B38" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E38" s="4" t="s">
+      <c r="D40" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E40" s="4" t="s">
         <v>184</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D4A941-9B0F-4026-ABDD-AB8EE2A7598E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CCE3E70-5268-43B0-B2B8-B1D6F2A3C500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="210">
   <si>
     <t>id</t>
   </si>
@@ -649,6 +649,36 @@
   </si>
   <si>
     <t>25 Images. Name the Cartoon from the Silhouette, also the Famous Artwork, and the Artwork's Artist.</t>
+  </si>
+  <si>
+    <t>quizzes/Artist_an_Album_(Pixelated)_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/Artist_an_Album_(Distorted)_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Q0041</t>
+  </si>
+  <si>
+    <t>RH-GK041</t>
+  </si>
+  <si>
+    <t>Q0042</t>
+  </si>
+  <si>
+    <t>RH-GK042</t>
+  </si>
+  <si>
+    <t>Artist an Album (Pixelated)</t>
+  </si>
+  <si>
+    <t>Artist an Album (Distorted)</t>
+  </si>
+  <si>
+    <t>25 Images.Name both the Artist and Album - the Album art has been pixelated.</t>
+  </si>
+  <si>
+    <t>25 Images.Name both the Artist and Album - the Album art has been distorted.</t>
   </si>
 </sst>
 </file>
@@ -1045,7 +1075,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -1753,6 +1783,40 @@
         <v>195</v>
       </c>
     </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CCE3E70-5268-43B0-B2B8-B1D6F2A3C500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3545FEE-4367-4E7B-9B3A-7F69A7603AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="218">
   <si>
     <t>id</t>
   </si>
@@ -679,6 +679,30 @@
   </si>
   <si>
     <t>25 Images.Name both the Artist and Album - the Album art has been distorted.</t>
+  </si>
+  <si>
+    <t>Johns</t>
+  </si>
+  <si>
+    <t>Johns (Tiled)</t>
+  </si>
+  <si>
+    <t>Q0043</t>
+  </si>
+  <si>
+    <t>Q0044</t>
+  </si>
+  <si>
+    <t>RH-GK043</t>
+  </si>
+  <si>
+    <t>RH-GK044</t>
+  </si>
+  <si>
+    <t>quizzes/Johns_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/Johns_(Tiled)_Quiz.pdf</t>
   </si>
 </sst>
 </file>
@@ -719,7 +743,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -730,6 +754,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF221C00"/>
         <bgColor rgb="FF221C00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -760,7 +790,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -773,6 +803,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1075,7 +1109,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -1614,37 +1648,37 @@
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C32" s="3" t="s">
+      <c r="B32" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="C32" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="7" t="s">
         <v>141</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>146</v>
+        <v>216</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C33" s="3" t="s">
+      <c r="B33" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="C33" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="D33" s="4" t="s">
-        <v>150</v>
+      <c r="D33" s="7" t="s">
+        <v>188</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>151</v>
+        <v>217</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
@@ -1652,16 +1686,16 @@
         <v>154</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>155</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
@@ -1669,16 +1703,16 @@
         <v>159</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>160</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
@@ -1686,16 +1720,16 @@
         <v>163</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>164</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>187</v>
+        <v>157</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
@@ -1703,16 +1737,16 @@
         <v>167</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>168</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
@@ -1720,16 +1754,16 @@
         <v>172</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>173</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
@@ -1737,16 +1771,16 @@
         <v>177</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>178</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
@@ -1754,16 +1788,16 @@
         <v>179</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>180</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
@@ -1771,16 +1805,16 @@
         <v>196</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>197</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
@@ -1788,16 +1822,16 @@
         <v>202</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>203</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
@@ -1805,15 +1839,49 @@
         <v>204</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>205</v>
       </c>
       <c r="D43" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E45" s="4" t="s">
         <v>201</v>
       </c>
     </row>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3545FEE-4367-4E7B-9B3A-7F69A7603AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85637424-B680-41E4-9FEB-A7DD4046C6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="223">
   <si>
     <t>id</t>
   </si>
@@ -703,6 +703,21 @@
   </si>
   <si>
     <t>quizzes/Johns_(Tiled)_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Q0045</t>
+  </si>
+  <si>
+    <t>RH-GK045</t>
+  </si>
+  <si>
+    <t>Lego-ed Movies</t>
+  </si>
+  <si>
+    <t>25 Images.Name the film from the poster recreated in Lego.</t>
+  </si>
+  <si>
+    <t>quizzes/Lego-ed_Movies_Quiz.pdf</t>
   </si>
 </sst>
 </file>
@@ -1109,7 +1124,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -1885,6 +1900,23 @@
         <v>201</v>
       </c>
     </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85637424-B680-41E4-9FEB-A7DD4046C6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89530DB9-BA6A-4ADF-9F02-D66855E8C27C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quizzes" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="318">
   <si>
     <t>id</t>
   </si>
@@ -675,12 +676,6 @@
     <t>Artist an Album (Distorted)</t>
   </si>
   <si>
-    <t>25 Images.Name both the Artist and Album - the Album art has been pixelated.</t>
-  </si>
-  <si>
-    <t>25 Images.Name both the Artist and Album - the Album art has been distorted.</t>
-  </si>
-  <si>
     <t>Johns</t>
   </si>
   <si>
@@ -714,10 +709,301 @@
     <t>Lego-ed Movies</t>
   </si>
   <si>
-    <t>25 Images.Name the film from the poster recreated in Lego.</t>
-  </si>
-  <si>
     <t>quizzes/Lego-ed_Movies_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Q0046</t>
+  </si>
+  <si>
+    <t>RH-GK046</t>
+  </si>
+  <si>
+    <t>quizzes/Music_Videos_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Music Videos</t>
+  </si>
+  <si>
+    <t>25 Images. Name the Artist and Track from the Image of the Music Video</t>
+  </si>
+  <si>
+    <t>25 Images. Name the film from the poster recreated in Lego.</t>
+  </si>
+  <si>
+    <t>25 Images. Name both the Artist and Album - the Album art has been distorted.</t>
+  </si>
+  <si>
+    <t>25 Images. Name both the Artist and Album - the Album art has been pixelated.</t>
+  </si>
+  <si>
+    <t>Q0047</t>
+  </si>
+  <si>
+    <t>RH-GK047</t>
+  </si>
+  <si>
+    <t>Rebus British TV Shows</t>
+  </si>
+  <si>
+    <t>quizzes/Rebus_British_TV_Shows_Quiz</t>
+  </si>
+  <si>
+    <t>25 Rebus Images of British TV Shows. Each image is a visual pun or clue that represents a band name.</t>
+  </si>
+  <si>
+    <t>Q0048</t>
+  </si>
+  <si>
+    <t>RH-GK048</t>
+  </si>
+  <si>
+    <t>Big Down Under</t>
+  </si>
+  <si>
+    <t>25 Images. All Famous Australians with two exceptions.</t>
+  </si>
+  <si>
+    <t>quizzes/Big_Down_Under_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Q0049</t>
+  </si>
+  <si>
+    <t>RH-GK049</t>
+  </si>
+  <si>
+    <t>25 Images. Name the Brand.</t>
+  </si>
+  <si>
+    <t>Brands</t>
+  </si>
+  <si>
+    <t>quizzes/Brands_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Q0050</t>
+  </si>
+  <si>
+    <t>RH-GK050</t>
+  </si>
+  <si>
+    <t>Simpson</t>
+  </si>
+  <si>
+    <t>25 Images. The pictures show famous people who have appeared in The Simpsons: some voiced a character, some appeared as themselves, and some were represented in Simpsons style.</t>
+  </si>
+  <si>
+    <t>quizzes/Simpsons_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/Papa_Was_A_Rollin_Stone_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Q0051</t>
+  </si>
+  <si>
+    <t>RH-GK051</t>
+  </si>
+  <si>
+    <t>Papa Was A Rollin' Stone</t>
+  </si>
+  <si>
+    <t>25 Images.Name the Pictured Celebrity and their Famous Parent(s).</t>
+  </si>
+  <si>
+    <t>Q0052</t>
+  </si>
+  <si>
+    <t>RH-GK052</t>
+  </si>
+  <si>
+    <t>Q0053</t>
+  </si>
+  <si>
+    <t>RH-GK053</t>
+  </si>
+  <si>
+    <t>Q0054</t>
+  </si>
+  <si>
+    <t>RH-GK054</t>
+  </si>
+  <si>
+    <t>quizzes/2024_Deaths_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>2024 Deaths</t>
+  </si>
+  <si>
+    <t>25 Images.Name the Celebrity that passed in 2024.</t>
+  </si>
+  <si>
+    <t>25 Images.Name the Celebrity that passed in 2025.</t>
+  </si>
+  <si>
+    <t>25 Images.Name the Celebrity that passed in 2025 (zombie filtered).</t>
+  </si>
+  <si>
+    <t>2025 Deaths</t>
+  </si>
+  <si>
+    <t>2025 Deaths (zombied)</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\25 - Ace Frehley.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\01 - Wayne Osmond.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\02 - The Vivienne.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\03 - Paul Danan.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\04 - Chris Rea.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\05 - Pauline Collins.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\06 - Prunella Scales.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\07 - Jilly Cooper.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\08 - Patricia Routledge.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\09 - Jane Goodall.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\10 - Ricky Hatton.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\11 - Katharine Duchess of Kent.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\12 - Angela Mortimer Barrett.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\13 - Diogo Jota.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\14 - Kim Woodburn.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\15 - Robert Redford.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\16 - Brian Wilson.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\17 - Roberta Flack.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\18 - Val Kilmer.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\19 - Terrence Stamp.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\20 - Gene Hackman.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\21 - Felix Baumgartner.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\22 - Hulk Hogan.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\23 - Charlie Kirk.png</t>
+  </si>
+  <si>
+    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\24 - Diane Keaton.png</t>
+  </si>
+  <si>
+    <t>American singer and member of the Osmond family.</t>
+  </si>
+  <si>
+    <t>British drag performer and winner of RuPaul’s Drag Race UK.</t>
+  </si>
+  <si>
+    <t>British reality TV personality known for Celebrity Love Island and Hollyoaks.</t>
+  </si>
+  <si>
+    <t>British singer‑songwriter known for hits like The Road to Hell.</t>
+  </si>
+  <si>
+    <t>British actress known for Shirley Valentine and Upstairs, Downstairs.</t>
+  </si>
+  <si>
+    <t>British actress famous for Fawlty Towers and A Question of Attribution.</t>
+  </si>
+  <si>
+    <t>British author known for romantic fiction and the Rutshire Chronicles.</t>
+  </si>
+  <si>
+    <t>British actress best known for Keeping Up Appearances.</t>
+  </si>
+  <si>
+    <t>World‑renowned primatologist and conservationist known for her work with chimpanzees.</t>
+  </si>
+  <si>
+    <t>British former world champion boxer nicknamed “The Hitman.”</t>
+  </si>
+  <si>
+    <t>Member of the British royal family and wife of Prince Edward, Duke of Kent.</t>
+  </si>
+  <si>
+    <t>British tennis champion and former world No. 1.</t>
+  </si>
+  <si>
+    <t>Portuguese footballer who played for Liverpool and the Portugal national team.</t>
+  </si>
+  <si>
+    <t>British TV personality known for How Clean Is Your House?</t>
+  </si>
+  <si>
+    <t>American actor and director known for Butch Cassidy, The Sting and All the President’s Men.</t>
+  </si>
+  <si>
+    <t>American musician, co‑founder of The Beach Boys.</t>
+  </si>
+  <si>
+    <t>American singer known for Killing Me Softly and The First Time Ever I Saw Your Face.</t>
+  </si>
+  <si>
+    <t>American actor known for Top Gun, Batman Forever and Heat.</t>
+  </si>
+  <si>
+    <t>British actor known for Billy Budd, Superman and The Limey.</t>
+  </si>
+  <si>
+    <t>American actor known for The French Connection, Hoosiers and Unforgiven.</t>
+  </si>
+  <si>
+    <t>Austrian skydiver famous for his record‑breaking Red Bull Stratos jump.</t>
+  </si>
+  <si>
+    <t>American professional wrestler and pop‑culture icon.</t>
+  </si>
+  <si>
+    <t>American political commentator and activist.</t>
+  </si>
+  <si>
+    <t>American actress known for Annie Hall, Something’s Gotta Give and The Godfather Part III.</t>
+  </si>
+  <si>
+    <t>American guitarist and founding member of Kiss.</t>
+  </si>
+  <si>
+    <t>quizzes/2025_Deaths_(zombied)_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/2025_Deaths_Quiz.pdf</t>
   </si>
 </sst>
 </file>
@@ -758,7 +1044,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -774,6 +1060,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -805,7 +1097,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -822,6 +1114,10 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1124,7 +1420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -1667,7 +1963,7 @@
         <v>144</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>145</v>
@@ -1676,7 +1972,7 @@
         <v>141</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -1684,7 +1980,7 @@
         <v>147</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>148</v>
@@ -1693,7 +1989,7 @@
         <v>188</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
@@ -1868,16 +2164,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>206</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>200</v>
@@ -1885,16 +2181,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>207</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>201</v>
@@ -1902,19 +2198,172 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B46" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="C46" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="D46" s="4" t="s">
+      <c r="B47" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="D47" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="E47" s="4" t="s">
         <v>222</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -1923,4 +2372,217 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43F4F385-FAEF-4D66-B010-82F0D8ECA806}">
+  <dimension ref="A1:L25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>267</v>
+      </c>
+      <c r="L1" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>268</v>
+      </c>
+      <c r="L2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>270</v>
+      </c>
+      <c r="L4" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>271</v>
+      </c>
+      <c r="L5" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>272</v>
+      </c>
+      <c r="L6" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>273</v>
+      </c>
+      <c r="L7" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>274</v>
+      </c>
+      <c r="L8" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>275</v>
+      </c>
+      <c r="L9" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>276</v>
+      </c>
+      <c r="L10" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>277</v>
+      </c>
+      <c r="L11" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>278</v>
+      </c>
+      <c r="L12" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>279</v>
+      </c>
+      <c r="L13" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>280</v>
+      </c>
+      <c r="L14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>281</v>
+      </c>
+      <c r="L15" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>282</v>
+      </c>
+      <c r="L16" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>283</v>
+      </c>
+      <c r="L17" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>284</v>
+      </c>
+      <c r="L18" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>285</v>
+      </c>
+      <c r="L19" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>286</v>
+      </c>
+      <c r="L20" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>287</v>
+      </c>
+      <c r="L21" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>288</v>
+      </c>
+      <c r="L22" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>289</v>
+      </c>
+      <c r="L23" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>290</v>
+      </c>
+      <c r="L24" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>266</v>
+      </c>
+      <c r="L25" t="s">
+        <v>315</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:A25">
+    <sortCondition ref="A1:A25"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89530DB9-BA6A-4ADF-9F02-D66855E8C27C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3298C12A-54E0-469A-8974-F7E0A7327118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -745,9 +745,6 @@
     <t>Rebus British TV Shows</t>
   </si>
   <si>
-    <t>quizzes/Rebus_British_TV_Shows_Quiz</t>
-  </si>
-  <si>
     <t>25 Rebus Images of British TV Shows. Each image is a visual pun or clue that represents a band name.</t>
   </si>
   <si>
@@ -1004,6 +1001,9 @@
   </si>
   <si>
     <t>quizzes/2025_Deaths_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/Rebus_British_TV_Shows_Quiz.pdf</t>
   </si>
 </sst>
 </file>
@@ -2241,129 +2241,129 @@
         <v>229</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>231</v>
+        <v>317</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="D49" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="D49" s="4" t="s">
+      <c r="E49" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="D50" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="E50" s="4" t="s">
         <v>241</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="D51" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D51" s="4" t="s">
+      <c r="E51" s="4" t="s">
         <v>246</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="D52" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>252</v>
-      </c>
       <c r="E52" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="C53" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="B53" s="9" t="s">
+      <c r="D53" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="C53" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>261</v>
-      </c>
       <c r="E53" s="9" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C54" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="B54" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>256</v>
-      </c>
       <c r="D54" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="C55" s="8" t="s">
         <v>257</v>
       </c>
-      <c r="B55" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="C55" s="8" t="s">
-        <v>258</v>
-      </c>
       <c r="D55" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -2381,202 +2381,202 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="L10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="L11" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L12" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L14" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L15" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L16" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L18" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L19" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L20" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L21" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L22" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L23" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L24" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L25" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3298C12A-54E0-469A-8974-F7E0A7327118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E919C2-9266-431C-91C7-07E8F621E913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="328">
   <si>
     <t>id</t>
   </si>
@@ -1004,6 +1004,36 @@
   </si>
   <si>
     <t>quizzes/Rebus_British_TV_Shows_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Q0055</t>
+  </si>
+  <si>
+    <t>RH-GK055</t>
+  </si>
+  <si>
+    <t>quizzes/Dragons,_Fairies,_Witches_and_Wizards_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Dragons, Fairies, Witches and Wizards</t>
+  </si>
+  <si>
+    <t>28 Images.Name the film or franchise the image belongs to.</t>
+  </si>
+  <si>
+    <t>Q0056</t>
+  </si>
+  <si>
+    <t>RH-GK056</t>
+  </si>
+  <si>
+    <t>It's a Puppet</t>
+  </si>
+  <si>
+    <t>25 Images.Name the Puppet.</t>
+  </si>
+  <si>
+    <t>quizzes/It's_a_Puppet_Quiz.pdf</t>
   </si>
 </sst>
 </file>
@@ -1420,7 +1450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -2364,6 +2394,40 @@
       </c>
       <c r="E55" s="9" t="s">
         <v>315</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>327</v>
       </c>
     </row>
   </sheetData>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E919C2-9266-431C-91C7-07E8F621E913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A49C3E-DFFF-4BAE-BE3E-3CE6673AB8D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="333">
   <si>
     <t>id</t>
   </si>
@@ -1034,6 +1034,21 @@
   </si>
   <si>
     <t>quizzes/It's_a_Puppet_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Q0057</t>
+  </si>
+  <si>
+    <t>RH-GK057</t>
+  </si>
+  <si>
+    <t>Number Ones</t>
+  </si>
+  <si>
+    <t>quizzes/Number_Ones_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>30 Images.All of these are UK Number One singles containing the string “ONE” somewhere in the title; the rest of each title has been encoded using V for vowels and C for consonants. Artist initials and the year are provided—name the song.</t>
   </si>
 </sst>
 </file>
@@ -1450,7 +1465,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E57"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -2430,6 +2446,23 @@
         <v>327</v>
       </c>
     </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>331</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2440,6 +2473,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43F4F385-FAEF-4D66-B010-82F0D8ECA806}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75A49C3E-DFFF-4BAE-BE3E-3CE6673AB8D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C94612D-A2FB-415D-A5A1-6F4EAF73C963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22860" yWindow="-16335" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quizzes" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
@@ -50,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="313">
   <si>
     <t>id</t>
   </si>
@@ -847,156 +846,6 @@
     <t>2025 Deaths (zombied)</t>
   </si>
   <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\25 - Ace Frehley.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\01 - Wayne Osmond.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\02 - The Vivienne.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\03 - Paul Danan.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\04 - Chris Rea.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\05 - Pauline Collins.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\06 - Prunella Scales.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\07 - Jilly Cooper.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\08 - Patricia Routledge.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\09 - Jane Goodall.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\10 - Ricky Hatton.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\11 - Katharine Duchess of Kent.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\12 - Angela Mortimer Barrett.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\13 - Diogo Jota.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\14 - Kim Woodburn.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\15 - Robert Redford.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\16 - Brian Wilson.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\17 - Roberta Flack.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\18 - Val Kilmer.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\19 - Terrence Stamp.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\20 - Gene Hackman.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\21 - Felix Baumgartner.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\22 - Hulk Hogan.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\23 - Charlie Kirk.png</t>
-  </si>
-  <si>
-    <t>C:\Users\Lenovo\Documents\Pub Quiz\02 - Pictures\01 - Cleaned\Dead 2025\Pictures\24 - Diane Keaton.png</t>
-  </si>
-  <si>
-    <t>American singer and member of the Osmond family.</t>
-  </si>
-  <si>
-    <t>British drag performer and winner of RuPaul’s Drag Race UK.</t>
-  </si>
-  <si>
-    <t>British reality TV personality known for Celebrity Love Island and Hollyoaks.</t>
-  </si>
-  <si>
-    <t>British singer‑songwriter known for hits like The Road to Hell.</t>
-  </si>
-  <si>
-    <t>British actress known for Shirley Valentine and Upstairs, Downstairs.</t>
-  </si>
-  <si>
-    <t>British actress famous for Fawlty Towers and A Question of Attribution.</t>
-  </si>
-  <si>
-    <t>British author known for romantic fiction and the Rutshire Chronicles.</t>
-  </si>
-  <si>
-    <t>British actress best known for Keeping Up Appearances.</t>
-  </si>
-  <si>
-    <t>World‑renowned primatologist and conservationist known for her work with chimpanzees.</t>
-  </si>
-  <si>
-    <t>British former world champion boxer nicknamed “The Hitman.”</t>
-  </si>
-  <si>
-    <t>Member of the British royal family and wife of Prince Edward, Duke of Kent.</t>
-  </si>
-  <si>
-    <t>British tennis champion and former world No. 1.</t>
-  </si>
-  <si>
-    <t>Portuguese footballer who played for Liverpool and the Portugal national team.</t>
-  </si>
-  <si>
-    <t>British TV personality known for How Clean Is Your House?</t>
-  </si>
-  <si>
-    <t>American actor and director known for Butch Cassidy, The Sting and All the President’s Men.</t>
-  </si>
-  <si>
-    <t>American musician, co‑founder of The Beach Boys.</t>
-  </si>
-  <si>
-    <t>American singer known for Killing Me Softly and The First Time Ever I Saw Your Face.</t>
-  </si>
-  <si>
-    <t>American actor known for Top Gun, Batman Forever and Heat.</t>
-  </si>
-  <si>
-    <t>British actor known for Billy Budd, Superman and The Limey.</t>
-  </si>
-  <si>
-    <t>American actor known for The French Connection, Hoosiers and Unforgiven.</t>
-  </si>
-  <si>
-    <t>Austrian skydiver famous for his record‑breaking Red Bull Stratos jump.</t>
-  </si>
-  <si>
-    <t>American professional wrestler and pop‑culture icon.</t>
-  </si>
-  <si>
-    <t>American political commentator and activist.</t>
-  </si>
-  <si>
-    <t>American actress known for Annie Hall, Something’s Gotta Give and The Godfather Part III.</t>
-  </si>
-  <si>
-    <t>American guitarist and founding member of Kiss.</t>
-  </si>
-  <si>
     <t>quizzes/2025_Deaths_(zombied)_Quiz.pdf</t>
   </si>
   <si>
@@ -1049,6 +898,96 @@
   </si>
   <si>
     <t>30 Images.All of these are UK Number One singles containing the string “ONE” somewhere in the title; the rest of each title has been encoded using V for vowels and C for consonants. Artist initials and the year are provided—name the song.</t>
+  </si>
+  <si>
+    <t>25 Images. The Pictures show a complete jigsaw - Unfortunately a Character has been mixed up with an Actor that either voice or plays them.  Name both the Actor and the Character.</t>
+  </si>
+  <si>
+    <t>Mixed Up Jigsaws</t>
+  </si>
+  <si>
+    <t>Q0058</t>
+  </si>
+  <si>
+    <t>RH-GK058</t>
+  </si>
+  <si>
+    <t>quizzes/Mixed_Up_Jigsaws_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/Captains_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Q0059</t>
+  </si>
+  <si>
+    <t>RH-GK059</t>
+  </si>
+  <si>
+    <t>Captains</t>
+  </si>
+  <si>
+    <t>25 Images of Actors, Charaters and Dingbats all Captain themed.</t>
+  </si>
+  <si>
+    <t>Q0060</t>
+  </si>
+  <si>
+    <t>RH-GK060</t>
+  </si>
+  <si>
+    <t>quizzes/Artists_-_One_Changed_Letter_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>25 Images. Each image represents a music artist whose name has had one letter changed. The changed letter is shown above the picture, and the replacement letter below. The picture itself is a literal, graphical representation of the changed name. Your task is to identify the original artist.</t>
+  </si>
+  <si>
+    <t>Artists - One Changed Letter</t>
+  </si>
+  <si>
+    <t>Q0061</t>
+  </si>
+  <si>
+    <t>RH-GK061</t>
+  </si>
+  <si>
+    <t>quizzes/UK_Sitcoms_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>25 Images. Name the Sitcom. Bonus if you take the first letter of each answer and rearange them you get a British Comedian and Film they stared in. Answer: Sid James, Carry On Regardless.</t>
+  </si>
+  <si>
+    <t>Hiddden Anagram: UK Sitcoms</t>
+  </si>
+  <si>
+    <t>Q0062</t>
+  </si>
+  <si>
+    <t>RH-GK062</t>
+  </si>
+  <si>
+    <t>25 Images. Name the Celebrity. Bonus if you take the first letter of each answer and rearange them you get Actor and Film they stared in. Answer: Leonardo DiCaprio, Inception.</t>
+  </si>
+  <si>
+    <t>Hiddden Anagram: Celebrities 01</t>
+  </si>
+  <si>
+    <t>Q0063</t>
+  </si>
+  <si>
+    <t>Hiddden Anagram: Celebrities 02</t>
+  </si>
+  <si>
+    <t>RH-GK063</t>
+  </si>
+  <si>
+    <t>25 Images. Name the Celebrity. Bonus if you take the first letter of each answer and rearange them you a Film. Answer: The Rocky Horror Picture Show.</t>
+  </si>
+  <si>
+    <t>quizzes/Celebrities_01_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/Celebrities_02_Quiz.pdf</t>
   </si>
 </sst>
 </file>
@@ -1089,7 +1028,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1111,6 +1050,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1142,7 +1087,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1163,6 +1108,10 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1466,13 +1415,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="93.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="201" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="42.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
@@ -2290,7 +2239,7 @@
         <v>231</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>317</v>
+        <v>267</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
@@ -2392,7 +2341,7 @@
         <v>261</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>316</v>
+        <v>266</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.2">
@@ -2409,58 +2358,160 @@
         <v>262</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>315</v>
+        <v>265</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A56" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="B56" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>320</v>
+      <c r="A56" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A57" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="B57" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>327</v>
+      <c r="A57" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>276</v>
+      </c>
+      <c r="E57" s="11" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A58" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>331</v>
+      <c r="A58" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="E58" s="11" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="E59" s="11" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>291</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="E60" s="11" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>301</v>
+      </c>
+      <c r="E62" s="11" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="E63" s="11" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A64" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="E64" s="11" t="s">
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -2469,218 +2520,4 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43F4F385-FAEF-4D66-B010-82F0D8ECA806}">
-  <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>266</v>
-      </c>
-      <c r="L1" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>267</v>
-      </c>
-      <c r="L2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>268</v>
-      </c>
-      <c r="L3" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>269</v>
-      </c>
-      <c r="L4" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>270</v>
-      </c>
-      <c r="L5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>271</v>
-      </c>
-      <c r="L6" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>272</v>
-      </c>
-      <c r="L7" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>273</v>
-      </c>
-      <c r="L8" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>274</v>
-      </c>
-      <c r="L9" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>275</v>
-      </c>
-      <c r="L10" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>276</v>
-      </c>
-      <c r="L11" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>277</v>
-      </c>
-      <c r="L12" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>278</v>
-      </c>
-      <c r="L13" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>279</v>
-      </c>
-      <c r="L14" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>280</v>
-      </c>
-      <c r="L15" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>281</v>
-      </c>
-      <c r="L16" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>282</v>
-      </c>
-      <c r="L17" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>283</v>
-      </c>
-      <c r="L18" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>284</v>
-      </c>
-      <c r="L19" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>285</v>
-      </c>
-      <c r="L20" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>286</v>
-      </c>
-      <c r="L21" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>287</v>
-      </c>
-      <c r="L22" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>288</v>
-      </c>
-      <c r="L23" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>289</v>
-      </c>
-      <c r="L24" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>265</v>
-      </c>
-      <c r="L25" t="s">
-        <v>314</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:A25">
-    <sortCondition ref="A1:A25"/>
-  </sortState>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C94612D-A2FB-415D-A5A1-6F4EAF73C963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0055270-123E-4FDA-BE34-49D6C4E76293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22860" yWindow="-16335" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quizzes" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="316">
   <si>
     <t>id</t>
   </si>
@@ -988,6 +988,15 @@
   </si>
   <si>
     <t>quizzes/Celebrities_02_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>free</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -1087,7 +1096,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1112,6 +1121,16 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1415,18 +1434,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:E64"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F64"/>
+  <sheetFormatPr defaultColWidth="23.28515625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="201" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="42.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="16384" width="23.28515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1439,11 +1453,14 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="12" t="s">
+        <v>313</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -1456,11 +1473,14 @@
       <c r="D2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="13" t="s">
+        <v>315</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
@@ -1473,11 +1493,14 @@
       <c r="D3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>13</v>
       </c>
@@ -1490,11 +1513,14 @@
       <c r="D4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>17</v>
       </c>
@@ -1507,11 +1533,14 @@
       <c r="D5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
@@ -1524,11 +1553,14 @@
       <c r="D6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>31</v>
       </c>
@@ -1541,11 +1573,14 @@
       <c r="D7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>32</v>
       </c>
@@ -1558,11 +1593,14 @@
       <c r="D8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>33</v>
       </c>
@@ -1575,11 +1613,14 @@
       <c r="D9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>34</v>
       </c>
@@ -1592,11 +1633,14 @@
       <c r="D10" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>40</v>
       </c>
@@ -1609,11 +1653,14 @@
       <c r="D11" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>41</v>
       </c>
@@ -1626,11 +1673,14 @@
       <c r="D12" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>42</v>
       </c>
@@ -1643,11 +1693,14 @@
       <c r="D13" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>43</v>
       </c>
@@ -1660,11 +1713,14 @@
       <c r="D14" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>66</v>
       </c>
@@ -1677,11 +1733,14 @@
       <c r="D15" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>71</v>
       </c>
@@ -1694,11 +1753,14 @@
       <c r="D16" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>75</v>
       </c>
@@ -1711,11 +1773,14 @@
       <c r="D17" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>81</v>
       </c>
@@ -1728,11 +1793,14 @@
       <c r="D18" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>82</v>
       </c>
@@ -1745,11 +1813,14 @@
       <c r="D19" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>88</v>
       </c>
@@ -1762,11 +1833,14 @@
       <c r="D20" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F20" s="4" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>94</v>
       </c>
@@ -1779,11 +1853,14 @@
       <c r="D21" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>99</v>
       </c>
@@ -1796,11 +1873,14 @@
       <c r="D22" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>103</v>
       </c>
@@ -1813,11 +1893,14 @@
       <c r="D23" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>110</v>
       </c>
@@ -1830,11 +1913,14 @@
       <c r="D24" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>112</v>
       </c>
@@ -1847,11 +1933,14 @@
       <c r="D25" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>119</v>
       </c>
@@ -1864,11 +1953,14 @@
       <c r="D26" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>122</v>
       </c>
@@ -1881,11 +1973,14 @@
       <c r="D27" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>126</v>
       </c>
@@ -1898,11 +1993,14 @@
       <c r="D28" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F28" s="4" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>130</v>
       </c>
@@ -1915,11 +2013,14 @@
       <c r="D29" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>135</v>
       </c>
@@ -1932,11 +2033,14 @@
       <c r="D30" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
         <v>137</v>
       </c>
@@ -1949,11 +2053,14 @@
       <c r="D31" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
         <v>144</v>
       </c>
@@ -1966,11 +2073,14 @@
       <c r="D32" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="15" t="s">
+        <v>314</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
         <v>147</v>
       </c>
@@ -1983,11 +2093,14 @@
       <c r="D33" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="15" t="s">
+        <v>314</v>
+      </c>
+      <c r="F33" s="4" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>154</v>
       </c>
@@ -2000,11 +2113,14 @@
       <c r="D34" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>159</v>
       </c>
@@ -2017,11 +2133,14 @@
       <c r="D35" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>163</v>
       </c>
@@ -2034,11 +2153,14 @@
       <c r="D36" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F36" s="4" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
         <v>167</v>
       </c>
@@ -2051,11 +2173,14 @@
       <c r="D37" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>172</v>
       </c>
@@ -2068,11 +2193,14 @@
       <c r="D38" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F38" s="4" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
         <v>177</v>
       </c>
@@ -2085,11 +2213,14 @@
       <c r="D39" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F39" s="4" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
         <v>179</v>
       </c>
@@ -2102,11 +2233,14 @@
       <c r="D40" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F40" s="4" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
         <v>196</v>
       </c>
@@ -2119,11 +2253,14 @@
       <c r="D41" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F41" s="4" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>202</v>
       </c>
@@ -2136,11 +2273,14 @@
       <c r="D42" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F42" s="4" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
         <v>204</v>
       </c>
@@ -2153,11 +2293,14 @@
       <c r="D43" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F43" s="4" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>210</v>
       </c>
@@ -2170,11 +2313,14 @@
       <c r="D44" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F44" s="4" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>211</v>
       </c>
@@ -2187,11 +2333,14 @@
       <c r="D45" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="E45" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F45" s="4" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
         <v>216</v>
       </c>
@@ -2204,11 +2353,14 @@
       <c r="D46" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F46" s="4" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
         <v>220</v>
       </c>
@@ -2221,11 +2373,14 @@
       <c r="D47" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F47" s="4" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
         <v>228</v>
       </c>
@@ -2238,11 +2393,14 @@
       <c r="D48" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F48" s="4" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
         <v>232</v>
       </c>
@@ -2255,11 +2413,14 @@
       <c r="D49" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="E49" s="4" t="s">
+      <c r="E49" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F49" s="4" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
         <v>237</v>
       </c>
@@ -2272,11 +2433,14 @@
       <c r="D50" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="E50" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F50" s="4" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
         <v>242</v>
       </c>
@@ -2289,11 +2453,14 @@
       <c r="D51" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="E51" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F51" s="4" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
         <v>248</v>
       </c>
@@ -2306,11 +2473,14 @@
       <c r="D52" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="E52" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="F52" s="4" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
         <v>252</v>
       </c>
@@ -2323,11 +2493,14 @@
       <c r="D53" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="E53" s="9" t="s">
+      <c r="E53" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="F53" s="9" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="8" t="s">
         <v>254</v>
       </c>
@@ -2340,11 +2513,14 @@
       <c r="D54" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="E54" s="9" t="s">
+      <c r="E54" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="F54" s="9" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="8" t="s">
         <v>256</v>
       </c>
@@ -2357,11 +2533,14 @@
       <c r="D55" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="E55" s="9" t="s">
+      <c r="E55" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="F55" s="9" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="10" t="s">
         <v>268</v>
       </c>
@@ -2374,11 +2553,14 @@
       <c r="D56" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="E56" s="11" t="s">
+      <c r="E56" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="F56" s="11" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="10" t="s">
         <v>273</v>
       </c>
@@ -2391,11 +2573,14 @@
       <c r="D57" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="E57" s="11" t="s">
+      <c r="E57" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="F57" s="11" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="10" t="s">
         <v>278</v>
       </c>
@@ -2408,11 +2593,14 @@
       <c r="D58" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="E58" s="11" t="s">
+      <c r="E58" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="F58" s="11" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="10" t="s">
         <v>285</v>
       </c>
@@ -2425,11 +2613,14 @@
       <c r="D59" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="E59" s="11" t="s">
+      <c r="E59" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="F59" s="11" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="10" t="s">
         <v>289</v>
       </c>
@@ -2442,11 +2633,14 @@
       <c r="D60" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="E60" s="11" t="s">
+      <c r="E60" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="F60" s="11" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="10" t="s">
         <v>293</v>
       </c>
@@ -2459,11 +2653,14 @@
       <c r="D61" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="E61" s="11" t="s">
+      <c r="E61" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="F61" s="11" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="10" t="s">
         <v>298</v>
       </c>
@@ -2476,11 +2673,14 @@
       <c r="D62" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="E62" s="11" t="s">
+      <c r="E62" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="F62" s="11" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="10" t="s">
         <v>303</v>
       </c>
@@ -2493,11 +2693,14 @@
       <c r="D63" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="E63" s="11" t="s">
+      <c r="E63" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="F63" s="11" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="10" t="s">
         <v>307</v>
       </c>
@@ -2510,7 +2713,10 @@
       <c r="D64" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="E64" s="11" t="s">
+      <c r="E64" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="F64" s="11" t="s">
         <v>312</v>
       </c>
     </row>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0055270-123E-4FDA-BE34-49D6C4E76293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5209952-6660-4FDB-88CF-2BF5733E7CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1437,7 +1437,9 @@
   <dimension ref="A1:F64"/>
   <sheetFormatPr defaultColWidth="23.28515625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="23.28515625" style="1"/>
+    <col min="1" max="5" width="23.28515625" style="1"/>
+    <col min="6" max="6" width="42.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="23.28515625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5209952-6660-4FDB-88CF-2BF5733E7CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A87534C7-3C0D-4251-AE64-07C5C1FA24AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="321">
   <si>
     <t>id</t>
   </si>
@@ -997,6 +997,21 @@
   </si>
   <si>
     <t>yes</t>
+  </si>
+  <si>
+    <t>Q0064</t>
+  </si>
+  <si>
+    <t>RH-GK064</t>
+  </si>
+  <si>
+    <t>Shared Role</t>
+  </si>
+  <si>
+    <t>12 Images. Name the Role and the two Actors who shared it.</t>
+  </si>
+  <si>
+    <t>quizzes/Shared_Role_Quiz.pdf</t>
   </si>
 </sst>
 </file>
@@ -1434,7 +1449,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultColWidth="23.28515625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="23.28515625" style="1"/>
@@ -2722,6 +2737,26 @@
         <v>312</v>
       </c>
     </row>
+    <row r="65" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>318</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="E65" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="F65" s="11" t="s">
+        <v>320</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A87534C7-3C0D-4251-AE64-07C5C1FA24AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D3585D2-9F34-432D-8D36-EDF9B90BB63A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="326">
   <si>
     <t>id</t>
   </si>
@@ -1012,6 +1012,21 @@
   </si>
   <si>
     <t>quizzes/Shared_Role_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Halloween (Dingbats)</t>
+  </si>
+  <si>
+    <t>Q0065</t>
+  </si>
+  <si>
+    <t>RH-GK065</t>
+  </si>
+  <si>
+    <t>25 Images of Halloween Dingbats. This is a joke, or Trick, round - there are no answers. They are all nonscience.</t>
+  </si>
+  <si>
+    <t>quizzes/Halloween_(Trick_or_Treat)_Quiz.pdf</t>
   </si>
 </sst>
 </file>
@@ -1111,7 +1126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1128,13 +1143,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1144,8 +1153,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1449,7 +1456,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultColWidth="23.28515625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="23.28515625" style="1"/>
@@ -1470,7 +1477,7 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="10" t="s">
         <v>313</v>
       </c>
       <c r="F1" s="2" t="s">
@@ -1490,7 +1497,7 @@
       <c r="D2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="11" t="s">
         <v>315</v>
       </c>
       <c r="F2" s="4" t="s">
@@ -1510,7 +1517,7 @@
       <c r="D3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F3" s="4" t="s">
@@ -1530,7 +1537,7 @@
       <c r="D4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -1550,7 +1557,7 @@
       <c r="D5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F5" s="4" t="s">
@@ -1570,7 +1577,7 @@
       <c r="D6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F6" s="4" t="s">
@@ -1590,7 +1597,7 @@
       <c r="D7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F7" s="4" t="s">
@@ -1610,7 +1617,7 @@
       <c r="D8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F8" s="4" t="s">
@@ -1630,7 +1637,7 @@
       <c r="D9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F9" s="4" t="s">
@@ -1650,7 +1657,7 @@
       <c r="D10" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F10" s="4" t="s">
@@ -1670,7 +1677,7 @@
       <c r="D11" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F11" s="4" t="s">
@@ -1690,7 +1697,7 @@
       <c r="D12" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F12" s="4" t="s">
@@ -1710,7 +1717,7 @@
       <c r="D13" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="14" t="s">
+      <c r="E13" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F13" s="4" t="s">
@@ -1730,7 +1737,7 @@
       <c r="D14" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="E14" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F14" s="4" t="s">
@@ -1750,7 +1757,7 @@
       <c r="D15" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F15" s="3" t="s">
@@ -1770,7 +1777,7 @@
       <c r="D16" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="E16" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -1790,7 +1797,7 @@
       <c r="D17" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -1810,7 +1817,7 @@
       <c r="D18" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="E18" s="14" t="s">
+      <c r="E18" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -1818,23 +1825,23 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="B19" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>92</v>
+      <c r="D19" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1842,19 +1849,19 @@
         <v>88</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>87</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="E20" s="14" t="s">
+        <v>193</v>
+      </c>
+      <c r="E20" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1862,19 +1869,19 @@
         <v>94</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>95</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="E21" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="E21" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1882,19 +1889,19 @@
         <v>99</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>100</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E22" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="E22" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1902,19 +1909,19 @@
         <v>103</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>104</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E23" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1922,19 +1929,19 @@
         <v>110</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>111</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E24" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="E24" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1942,19 +1949,19 @@
         <v>112</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>113</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="E25" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E25" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1962,19 +1969,19 @@
         <v>119</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>120</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="E26" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="E26" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -1982,19 +1989,19 @@
         <v>122</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>123</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="E27" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2002,19 +2009,19 @@
         <v>126</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>127</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="E28" s="14" t="s">
+        <v>190</v>
+      </c>
+      <c r="E28" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2022,19 +2029,19 @@
         <v>130</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>131</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="E29" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="E29" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2042,19 +2049,19 @@
         <v>135</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>136</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="E30" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="E30" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2062,79 +2069,79 @@
         <v>137</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>138</v>
       </c>
       <c r="D31" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="E31" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="F31" s="4" t="s">
+      <c r="E32" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="B32" s="7" t="s">
+    <row r="33" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B33" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="D32" s="7" t="s">
+      <c r="C33" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D33" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="E32" s="15" t="s">
-        <v>314</v>
-      </c>
-      <c r="F32" s="4" t="s">
+      <c r="E33" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F33" s="4" t="s">
         <v>214</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="E33" s="15" t="s">
-        <v>314</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>152</v>
+      <c r="B34" s="7" t="s">
+        <v>209</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D34" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="E34" s="14" t="s">
+      <c r="D34" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E34" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>146</v>
+        <v>215</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2142,19 +2149,19 @@
         <v>159</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>160</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="E35" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="E35" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2162,19 +2169,19 @@
         <v>163</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>164</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="E36" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="E36" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2182,19 +2189,19 @@
         <v>167</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>168</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="E37" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="E37" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2202,19 +2209,19 @@
         <v>172</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>173</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="E38" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="E38" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2222,19 +2229,19 @@
         <v>177</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>178</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="E39" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="E39" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2242,19 +2249,19 @@
         <v>179</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>180</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="E40" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="E40" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2262,19 +2269,19 @@
         <v>196</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>197</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E41" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="E41" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2282,19 +2289,19 @@
         <v>202</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>203</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="E42" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="E42" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2302,19 +2309,19 @@
         <v>204</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>205</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="E43" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="E43" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2322,19 +2329,19 @@
         <v>210</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>212</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="E44" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="E44" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2342,19 +2349,19 @@
         <v>211</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>213</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="E45" s="14" t="s">
+        <v>227</v>
+      </c>
+      <c r="E45" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2362,19 +2369,19 @@
         <v>216</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>217</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="E46" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="E46" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2382,19 +2389,19 @@
         <v>220</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>221</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="E47" s="14" t="s">
+        <v>225</v>
+      </c>
+      <c r="E47" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2402,19 +2409,19 @@
         <v>228</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>229</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="E48" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="E48" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>267</v>
+        <v>222</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2422,19 +2429,19 @@
         <v>232</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>233</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="E49" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="E49" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>236</v>
+        <v>267</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2442,19 +2449,19 @@
         <v>237</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>238</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="E50" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="E50" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2462,19 +2469,19 @@
         <v>242</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>243</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="E51" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="E51" s="12" t="s">
         <v>314</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2482,278 +2489,298 @@
         <v>248</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>249</v>
       </c>
       <c r="D52" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="E52" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="F52" s="4" t="s">
+      <c r="E53" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F53" s="4" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="B53" s="9" t="s">
+    <row r="54" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B54" s="8" t="s">
         <v>259</v>
       </c>
-      <c r="C53" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="D53" s="9" t="s">
+      <c r="C54" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D54" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="E53" s="16" t="s">
-        <v>314</v>
-      </c>
-      <c r="F53" s="9" t="s">
+      <c r="E54" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F54" s="8" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="8" t="s">
-        <v>254</v>
-      </c>
-      <c r="B54" s="9" t="s">
+    <row r="55" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B55" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="C54" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="D54" s="9" t="s">
+      <c r="C55" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="D55" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="E54" s="16" t="s">
-        <v>314</v>
-      </c>
-      <c r="F54" s="9" t="s">
+      <c r="E55" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F55" s="8" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="B55" s="9" t="s">
+    <row r="56" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B56" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="C55" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="D55" s="9" t="s">
+      <c r="C56" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D56" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="E55" s="16" t="s">
-        <v>314</v>
-      </c>
-      <c r="F55" s="9" t="s">
+      <c r="E56" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F56" s="8" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="B56" s="11" t="s">
+    <row r="57" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B57" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="C56" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="D56" s="11" t="s">
+      <c r="C57" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="D57" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="E56" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="F56" s="11" t="s">
+      <c r="E57" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F57" s="9" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="B57" s="11" t="s">
+    <row r="58" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B58" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="C57" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="D57" s="11" t="s">
+      <c r="C58" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D58" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="E57" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="F57" s="11" t="s">
+      <c r="E58" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F58" s="9" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="B58" s="11" t="s">
+    <row r="59" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B59" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="C58" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="D58" s="11" t="s">
+      <c r="C59" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="D59" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="E58" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="F58" s="11" t="s">
+      <c r="E59" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F59" s="9" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="10" t="s">
-        <v>285</v>
-      </c>
-      <c r="B59" s="11" t="s">
+    <row r="60" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B60" s="9" t="s">
         <v>284</v>
       </c>
-      <c r="C59" s="10" t="s">
-        <v>286</v>
-      </c>
-      <c r="D59" s="11" t="s">
+      <c r="C60" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D60" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="E59" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="F59" s="11" t="s">
+      <c r="E60" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F60" s="9" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="10" t="s">
-        <v>289</v>
-      </c>
-      <c r="B60" s="11" t="s">
+    <row r="61" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B61" s="9" t="s">
         <v>291</v>
       </c>
-      <c r="C60" s="10" t="s">
-        <v>290</v>
-      </c>
-      <c r="D60" s="11" t="s">
+      <c r="C61" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D61" s="9" t="s">
         <v>292</v>
       </c>
-      <c r="E60" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="F60" s="11" t="s">
+      <c r="E61" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F61" s="9" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="10" t="s">
-        <v>293</v>
-      </c>
-      <c r="B61" s="11" t="s">
+    <row r="62" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="B62" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="C61" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="D61" s="11" t="s">
+      <c r="C62" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D62" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="E61" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="F61" s="11" t="s">
+      <c r="E62" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F62" s="9" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="B62" s="11" t="s">
+    <row r="63" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B63" s="9" t="s">
         <v>302</v>
       </c>
-      <c r="C62" s="10" t="s">
-        <v>299</v>
-      </c>
-      <c r="D62" s="11" t="s">
+      <c r="C63" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D63" s="9" t="s">
         <v>301</v>
       </c>
-      <c r="E62" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="F62" s="11" t="s">
+      <c r="E63" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F63" s="9" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="B63" s="11" t="s">
+    <row r="64" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B64" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="C63" s="10" t="s">
-        <v>304</v>
-      </c>
-      <c r="D63" s="11" t="s">
+      <c r="C64" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="D64" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="E63" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="F63" s="11" t="s">
+      <c r="E64" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F64" s="9" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="B64" s="11" t="s">
+    <row r="65" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B65" s="9" t="s">
         <v>308</v>
       </c>
-      <c r="C64" s="10" t="s">
-        <v>309</v>
-      </c>
-      <c r="D64" s="11" t="s">
+      <c r="C65" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D65" s="9" t="s">
         <v>310</v>
       </c>
-      <c r="E64" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="F64" s="11" t="s">
+      <c r="E65" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F65" s="9" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="B65" s="11" t="s">
+    <row r="66" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B66" s="9" t="s">
         <v>318</v>
       </c>
-      <c r="C65" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="D65" s="11" t="s">
+      <c r="C66" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D66" s="9" t="s">
         <v>319</v>
       </c>
-      <c r="E65" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="F65" s="11" t="s">
+      <c r="E66" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F66" s="9" t="s">
         <v>320</v>
       </c>
     </row>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D3585D2-9F34-432D-8D36-EDF9B90BB63A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE4DF0D-3033-42D3-9728-BA0F5A9B58EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="331">
   <si>
     <t>id</t>
   </si>
@@ -1027,6 +1027,21 @@
   </si>
   <si>
     <t>quizzes/Halloween_(Trick_or_Treat)_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Q0066</t>
+  </si>
+  <si>
+    <t>RH-GK066</t>
+  </si>
+  <si>
+    <t>Doctors</t>
+  </si>
+  <si>
+    <t>25 Images. All famous Doctors or known for playing Doctors.</t>
+  </si>
+  <si>
+    <t>quizzes/Doctors_Quiz.pdf</t>
   </si>
 </sst>
 </file>
@@ -1456,7 +1471,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr defaultColWidth="23.28515625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="23.28515625" style="1"/>
@@ -2784,6 +2799,26 @@
         <v>320</v>
       </c>
     </row>
+    <row r="67" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>330</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFE4DF0D-3033-42D3-9728-BA0F5A9B58EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FAE75CB-C3F9-4078-8FDF-0F0564C641E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="336">
   <si>
     <t>id</t>
   </si>
@@ -1042,6 +1042,21 @@
   </si>
   <si>
     <t>quizzes/Doctors_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/Face_Swapped_Couples_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Q0067</t>
+  </si>
+  <si>
+    <t>RH-GK067</t>
+  </si>
+  <si>
+    <t>Face Swapped Couples</t>
+  </si>
+  <si>
+    <t>25 Images. Famous Couples where the face of one partner has been placed over the head of the other.</t>
   </si>
 </sst>
 </file>
@@ -1471,7 +1486,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr defaultColWidth="23.28515625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="23.28515625" style="1"/>
@@ -2819,6 +2834,26 @@
         <v>330</v>
       </c>
     </row>
+    <row r="68" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="E68" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="F68" s="9" t="s">
+        <v>331</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FAE75CB-C3F9-4078-8FDF-0F0564C641E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7853A11-A628-46FB-BE20-7008197F1958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="353">
   <si>
     <t>id</t>
   </si>
@@ -1057,6 +1057,57 @@
   </si>
   <si>
     <t>25 Images. Famous Couples where the face of one partner has been placed over the head of the other.</t>
+  </si>
+  <si>
+    <t>Q0068</t>
+  </si>
+  <si>
+    <t>RH-GK068</t>
+  </si>
+  <si>
+    <t>Q0069</t>
+  </si>
+  <si>
+    <t>RH-GK069</t>
+  </si>
+  <si>
+    <t>Q0070</t>
+  </si>
+  <si>
+    <t>RH-GK070</t>
+  </si>
+  <si>
+    <t>Q0071</t>
+  </si>
+  <si>
+    <t>RH-GK071</t>
+  </si>
+  <si>
+    <t>Football 01</t>
+  </si>
+  <si>
+    <t>Football 02</t>
+  </si>
+  <si>
+    <t>Football 03</t>
+  </si>
+  <si>
+    <t>Football 04</t>
+  </si>
+  <si>
+    <t>quizzes/Football_01_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/Football_02_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/Football_03_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/Football_04_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>25 Images. All images show UK football club badges with the names removed. Identify each club from the badge alone. Two of the images are not badges — they are photos of footballers who played at a World Cup. Name the club for each badge and name the player for each photo.</t>
   </si>
 </sst>
 </file>
@@ -1097,7 +1148,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1125,6 +1176,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1156,7 +1213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1183,6 +1240,11 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1486,7 +1548,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr defaultColWidth="23.28515625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="23.28515625" style="1"/>
@@ -2854,6 +2916,86 @@
         <v>331</v>
       </c>
     </row>
+    <row r="69" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="B69" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="C69" s="14" t="s">
+        <v>337</v>
+      </c>
+      <c r="D69" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="E69" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="F69" s="15" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="B70" s="15" t="s">
+        <v>345</v>
+      </c>
+      <c r="C70" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="D70" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="E70" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="F70" s="15" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="B71" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="C71" s="14" t="s">
+        <v>341</v>
+      </c>
+      <c r="D71" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="E71" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="F71" s="15" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="14" t="s">
+        <v>342</v>
+      </c>
+      <c r="B72" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="C72" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="D72" s="15" t="s">
+        <v>352</v>
+      </c>
+      <c r="E72" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="F72" s="15" t="s">
+        <v>351</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7853A11-A628-46FB-BE20-7008197F1958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8673A433-7494-4246-A379-F0C6B241566D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="362">
   <si>
     <t>id</t>
   </si>
@@ -1108,6 +1108,33 @@
   </si>
   <si>
     <t>25 Images. All images show UK football club badges with the names removed. Identify each club from the badge alone. Two of the images are not badges — they are photos of footballers who played at a World Cup. Name the club for each badge and name the player for each photo.</t>
+  </si>
+  <si>
+    <t>Q0072</t>
+  </si>
+  <si>
+    <t>RH-GK072</t>
+  </si>
+  <si>
+    <t>Q0073</t>
+  </si>
+  <si>
+    <t>RH-GK073</t>
+  </si>
+  <si>
+    <t>quizzes/Mix_Bag_01_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>quizzes/Mix_Bag_02_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Mix Bag 01</t>
+  </si>
+  <si>
+    <t>Mix Bag 02</t>
+  </si>
+  <si>
+    <t>25 Images. Nice and Simple, Name the image.</t>
   </si>
 </sst>
 </file>
@@ -1548,7 +1575,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr defaultColWidth="23.28515625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="23.28515625" style="1"/>
@@ -2996,6 +3023,46 @@
         <v>351</v>
       </c>
     </row>
+    <row r="73" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="E73" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="E74" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>358</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8673A433-7494-4246-A379-F0C6B241566D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3055E4AE-9DB3-469E-B835-DF15492F9C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="367">
   <si>
     <t>id</t>
   </si>
@@ -1135,6 +1135,21 @@
   </si>
   <si>
     <t>25 Images. Nice and Simple, Name the image.</t>
+  </si>
+  <si>
+    <t>Q0074</t>
+  </si>
+  <si>
+    <t>RH-GK074</t>
+  </si>
+  <si>
+    <t>quizzes/Synthetics_Quiz.pdf</t>
+  </si>
+  <si>
+    <t>Synthetics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 Images featuring famous robots, androids and synthetic characters from films, TV and sci‑fi. </t>
   </si>
 </sst>
 </file>
@@ -1575,7 +1590,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr defaultColWidth="23.28515625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="23.28515625" style="1"/>
@@ -3063,6 +3078,26 @@
         <v>358</v>
       </c>
     </row>
+    <row r="75" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="E75" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>364</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/quizzes-template.xlsx
+++ b/quizzes-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\GitHub\TableTops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3055E4AE-9DB3-469E-B835-DF15492F9C6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC94F40E-385A-4C17-98E4-8CFD8080ABDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
